--- a/astro-site/public/dl/pastry-shop-checklist-templates/13-food-temperature-log-receiving-log.xlsx
+++ b/astro-site/public/dl/pastry-shop-checklist-templates/13-food-temperature-log-receiving-log.xlsx
@@ -1029,7 +1029,7 @@
       <c r="D4" s="9" t="inlineStr">
         <is>
           <t>Dough retarder
-(36 to 41 °F)</t>
+(36 to 41 °F, in retard mode)</t>
         </is>
       </c>
       <c r="E4" s="32" t="n"/>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
-          <t>Minutes</t>
+          <t>Min. to 70 °F</t>
         </is>
       </c>
       <c r="N5" s="33" t="n"/>
@@ -1757,7 +1757,7 @@
     <row r="40" ht="21.8" customHeight="1">
       <c r="A40" s="19" t="inlineStr">
         <is>
-          <t>What to do if a temperature goes out of range: check that the door closes and the unit isn't overloaded, move the product to another unit, write the action on this same row and call the service technician. Kit rule: if TCS food has been above 41 °F for more than 2 h, or you don't know for how long, throw it out and log it as waste (only a written time-as-a-control procedure allows up to 4 h without refrigeration, FDA Food Code 3-501.19) (→ 10 Production Schedule &amp; Waste Log · sheet "Made vs Sold").</t>
+          <t>What to do if a temperature goes out of range: check that the door closes and the unit isn't overloaded, move the product to another unit, write the action on this same row and call the service technician. Kit rule: if TCS food has been above 41 °F for more than 2 h, or you don't know for how long, throw it out and log it as waste (time as a control, FDA Food Code 3-501.19, allows up to 4 h only with a written procedure set up in advance and the time marked on the product; it cannot be applied after the fact to a unit failure) (→ 10 Production Schedule &amp; Waste Log · sheet "Made vs Sold").</t>
         </is>
       </c>
       <c r="B40" s="35" t="n"/>
@@ -1775,7 +1775,7 @@
       <c r="N40" s="35" t="n"/>
       <c r="O40" s="36" t="n"/>
     </row>
-    <row r="41" ht="21.8" customHeight="1">
+    <row r="41" ht="37" customHeight="1">
       <c r="A41" s="37" t="n"/>
       <c r="B41" s="38" t="n"/>
       <c r="C41" s="38" t="n"/>
@@ -2403,7 +2403,7 @@
     <row r="38">
       <c r="A38" s="19" t="inlineStr">
         <is>
-          <t>Reject the delivery if: refrigerated TCS food arrives above 41 °F · shell eggs arrive in a truck with air above 45 °F · milk and cream arrive above 45 °F (allowed only where dairy law permits it and they are cooled to 41 °F within 4 h; FDA Food Code 3-202.11 and 3-501.14) · frozen food shows signs of thawing (frost, deformed block, liquid in the case) · the packaging is torn, open or wet · the expiration or best-by date is less than 2 days away · the truck is dirty or not cold · the invoice doesn't match what you receive. Log the reason, take a photo and notify the supplier the same day. Accepted with note: the goods are received, but the issue is written on the invoice before you sign it and photographed; the product is set aside, labeled, and not used until the supplier replies.</t>
+          <t>Reject the delivery if: refrigerated TCS food arrives above 41 °F · shell eggs arrive in a truck with air above 45 °F · milk and cream arrive above 45 °F (from 41 to 45 °F only where dairy law allows it, and then cool them to 41 °F within 4 h; FDA Food Code 3-202.11 and 3-501.14) · frozen food shows signs of thawing (frost, deformed block, liquid in the case) · the packaging is torn, open or wet · the expiration or best-by date is less than 2 days away · the truck is dirty or not cold · the invoice doesn't match what you receive. Log the reason, take a photo and notify the supplier the same day. Accepted with note: the goods are received, but the issue is written on the invoice before you sign it and photographed; the product is set aside, labeled, and not used until the supplier replies. The temperature column turns red only above 45 °F: above 41 and up to 45 °F, accept only shell eggs and milk or cream (where allowed) and note it in the reason column.</t>
         </is>
       </c>
       <c r="B38" s="35" t="n"/>
@@ -2421,7 +2421,7 @@
       <c r="A39" s="40" t="n"/>
       <c r="K39" s="41" t="n"/>
     </row>
-    <row r="40" ht="30" customHeight="1">
+    <row r="40" ht="42" customHeight="1">
       <c r="A40" s="37" t="n"/>
       <c r="B40" s="38" t="n"/>
       <c r="C40" s="38" t="n"/>
@@ -2466,7 +2466,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:G34">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="2">
-      <formula>41</formula>
+      <formula>45</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="D7" s="31" t="inlineStr">
         <is>
-          <t>Temper before using</t>
+          <t>Bring to room temperature before using</t>
         </is>
       </c>
     </row>
@@ -3384,10 +3384,10 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="22" customHeight="1">
+    <row r="10" ht="36" customHeight="1">
       <c r="A10" s="28" t="inlineStr">
         <is>
-          <t>Ganache truffles (cooked)</t>
+          <t>Cooked chocolate truffle cream (filling)</t>
         </is>
       </c>
       <c r="B10" s="29" t="inlineStr">
@@ -3534,7 +3534,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="43.6" customHeight="1">
+    <row r="17" ht="71" customHeight="1">
       <c r="A17" s="28" t="inlineStr">
         <is>
           <t>Baked viennoiserie</t>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="D17" s="31" t="inlineStr">
         <is>
-          <t>Next day: day-old discount or waste. Cream-filled: case at 41 °F or below (3-501.16)</t>
+          <t>Next day: day-old discount or waste. Custard-, cream- or cheese-filled pieces and savory items (quiche, ham &amp; cheese, empanadas): case at 41 °F or below (3-501.16), or time as a control with a written procedure (3-501.19: 4 h, then discard)</t>
         </is>
       </c>
     </row>
